--- a/tools/importer/reports/import-cra-public-file.report.xlsx
+++ b/tools/importer/reports/import-cra-public-file.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-08T17:15:47.276Z</t>
+    <t>2026-10-09T11:27:31.412Z</t>
   </si>
   <si>
     <t>Bradesco Bank</t>
@@ -73,7 +73,7 @@
     <t>bank-holidays</t>
   </si>
   <si>
-    <t>2026-10-09T01:38:04.138Z</t>
+    <t>2026-10-09T11:28:15.670Z</t>
   </si>
   <si>
     <t>Bank Holidays – Bradesco Bank</t>
@@ -94,7 +94,7 @@
     <t>cra-public-file</t>
   </si>
   <si>
-    <t>2026-10-09T02:37:20.746Z</t>
+    <t>2026-10-09T11:30:30.001Z</t>
   </si>
   <si>
     <t>CRA Public File – Bradesco Bank</t>
@@ -115,7 +115,7 @@
     <t>help</t>
   </si>
   <si>
-    <t>2026-10-09T01:53:09.734Z</t>
+    <t>2026-10-09T11:28:59.731Z</t>
   </si>
   <si>
     <t>How Can We Help? – Bradesco Bank</t>
@@ -136,13 +136,34 @@
     <t>other-disclosures</t>
   </si>
   <si>
-    <t>2026-10-09T02:14:51.356Z</t>
+    <t>2026-10-09T11:29:45.189Z</t>
   </si>
   <si>
     <t>Other disclosures – Bradesco Bank</t>
   </si>
   <si>
     <t>https://bradescobank.com/en/other-disclosures/</t>
+  </si>
+  <si>
+    <t>en/security.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-note","cards-note","cards-note","accordion-tips","columns-image-bleed"]</t>
+  </si>
+  <si>
+    <t>en/security</t>
+  </si>
+  <si>
+    <t>security</t>
+  </si>
+  <si>
+    <t>2026-10-09T02:57:45.360Z</t>
+  </si>
+  <si>
+    <t>Security – Bradesco Bank</t>
+  </si>
+  <si>
+    <t>https://bradescobank.com/en/security/</t>
   </si>
 </sst>
 </file>
@@ -531,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -699,6 +720,32 @@
         <v>43</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
